--- a/光伏配储项目/电价数据/2026/亭仔站.xlsx
+++ b/光伏配储项目/电价数据/2026/亭仔站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50989</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7206699999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56467</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.51619</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45343</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44807</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42326</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.2679</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21422</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25837</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07689</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06312</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03186</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05304</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03897</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04456</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01807</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01504</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.00167</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00354</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14522</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21298</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23615</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21354</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11501</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.00491</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00694</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.15504</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.19057</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22305</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.02949</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12241</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19378</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.26314</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.00945</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.23321</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.01205</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.4544</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5276799999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.4842</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.76387</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6151599999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.51217</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.13848</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.58846</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5427799999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.27053</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.50124</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.5042</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6161</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.57241</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43385</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.43697</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.34661</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6243500000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.43076</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7570399999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.27194</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.92789</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.54586</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52767</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50768</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5158200000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.51139</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39506</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47733</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42541</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5284</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.65507</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.75246</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44283</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.16803</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44834</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.08918000000000001</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.2637</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.21895</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.13794</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26948</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.25914</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.59101</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.21987</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27697</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27191</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.01771</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.26817</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.23125</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.15971</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23381</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.26026</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.2329</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.43932</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42369</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.26866</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.47482</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.7092200000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.99164</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.91488</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.27301</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.84722</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.43498</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38626</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.82709</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43831</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5986399999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4338399999999999</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40789</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.30393</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5672200000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.27669</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.27504</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.27036</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.26959</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.26727</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.13232</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.27325</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.03569</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.27772</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.28636</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.0709</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.14889</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20694</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.19416</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24825</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27975</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.28972</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.24902</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.21769</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.05470000000000001</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28322</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.47958</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.01116</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5014</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.28953</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3441</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.27063</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27414</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47899</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27414</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.28068</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26184</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19413</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10821</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11202</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08159000000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.25036</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21215</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.13163</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28847</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44892</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21393</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04383</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06116</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.27031</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.17597</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04197</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.008710000000000001</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21289</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.00065</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03134</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.04857</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07723999999999999</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.20175</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.1662</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20324</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.15145</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.1957</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14219</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.19978</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22726</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.27912</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.46993</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29218</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27548</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27657</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04073</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04514</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04027</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04001</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04268</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04502</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04352</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04553</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04643</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04712</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04643</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04677000000000001</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04761</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04682</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04584000000000001</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04799</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04647999999999999</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04796</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04917</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04877</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04646</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04729999999999999</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22002</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04644</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04888</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05166</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00212</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14709</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03758</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09886</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66442</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04263</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0459</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04509000000000001</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04181</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03235</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04067</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10694</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03741</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04108</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04125</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04117</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04367</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04106</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04048</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04327</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04033</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03896</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04343</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04107</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04215</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03997</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04265</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04304</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04643</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04601</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20236</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14482</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33776</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32295</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28359</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27354</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27369</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17437</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16063</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17326</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1496</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16132</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16071</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23962</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21613</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22873</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27201</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.26303</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.24505</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.26766</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>-0.01432</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.27846</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.25922</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.26008</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15729</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.16154</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.28249</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.26242</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.28349</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79108</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92003</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9280900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.90696</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31953</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9300900000000001</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6388200000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22894</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88951</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.58077</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37376</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06238</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.57384</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.82756</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.80976</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.8067000000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8813</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8930800000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5275</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43222</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48916</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2511</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.88007</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55177</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.66562</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54922</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.51028</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46118</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42942</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44488</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45203</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45326</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42239</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39683</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45133</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5897</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5968600000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.64474</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45477</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86509</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.11974</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.59942</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.58353</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.74963</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.20643</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43426</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.25985</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27333</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35329</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.0256</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.49966</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.50225</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.62088</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.69536</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.4152</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.45027</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.51189</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.44855</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16474</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28515</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26109</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20119</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27595</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.28948</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.25953</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.23038</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.2794</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.24908</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27494</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42815</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.2454</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59766</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8897699999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35759</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13653</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.71185</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80589</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65127</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5909500000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43988</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43442</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.23627</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.24116</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.26444</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.25356</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.24382</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.23469</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.2384</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.22768</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.24122</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.11504</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.22425</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.01498</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23824</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27372</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.01052</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.26699</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.23956</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.01545</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.23109</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26861</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.19438</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.25161</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29786</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38873</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.48713</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.43168</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.60788</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46574</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6842699999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46674</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43962</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42563</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32655</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42574</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.04836</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.04181</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23721</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14653</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14922</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15617</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14481</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14236</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14485</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14378</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25897</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14548</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26882</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14336</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05322</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11481</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11374</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14761</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14256</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14781</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28877</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.26636</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45143</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40366</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44182</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44127</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44622</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44547</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40428</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.3507</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.4046</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47036</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42544</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.23044</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.23072</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.22278</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.15409</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.06352000000000001</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.1188</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.14978</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.16863</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.17895</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.16286</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.15146</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.18342</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.18046</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.26868</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.28865</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44671</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45963</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24943</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42617</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38423</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.51288</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36064</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.22983</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.29345</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.21922</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.24719</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.24349</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26992</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.25962</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03308</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25457</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24999</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.21029</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07504999999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18447</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24498</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25322</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50603</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41635</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.77779</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46884</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.43636</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41732</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31021</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.27402</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.27622</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.27655</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28308</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28761</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34404</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.73677</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.4161</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40733</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64955</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.87715</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48741</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.48667</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46043</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34508</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26146</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13628</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19531</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24643</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.02733</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.13065</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.01866</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23762</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24796</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.00759</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14507</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.02265</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23411</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23691</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41752</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40873</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6309900000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6015199999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5750299999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46226</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.58823</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47798</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.72634</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40221</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48181</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41997</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49341</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.47457</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46664</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45761</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42154</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4198</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39827</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41151</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45082</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56135</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50095</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45098</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41563</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.30172</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.25082</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.24547</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.14569</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.15315</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04139</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03364</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.15252</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>-0.00024</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.10719</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.008029999999999999</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.03596</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48608</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.39484</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50844</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.42824</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.5761499999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.65863</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.64273</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.61514</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.67715</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5052300000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.49514</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.74287</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.6889700000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5642699999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.60538</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.40277</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46133</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.45841</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.45166</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5054999999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43028</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44322</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42532</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44202</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44459</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39464</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15854</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27337</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03829</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40847</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4529</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46388</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01511</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18511</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.39745</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39518</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39281</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36274</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.5516599999999999</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.5787899999999999</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24898</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23556</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23726</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24645</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25203</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.03992</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.12188</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.05706</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17616</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25948</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.04021</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14866</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15242</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.05914</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.01005</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.09553</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>-0.00632</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.11489</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>-0.04073</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>-0.02597</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35092</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19241</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.18505</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13104</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.14974</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04758</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01618</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00149</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04366</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04146</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.13864</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.19082</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27692</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22307</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.2237</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22456</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.2288</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26597</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.24875</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24204</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23329</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25285</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23569</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25406</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24268</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.2601</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.26149</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27587</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.21793</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.23829</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21619</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18581</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.08443000000000001</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.03836</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.23857</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.15572</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15541</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.15577</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.02352</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23351</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21654</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.20129</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16501</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15711</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.13232</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15674</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.18841</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.10938</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12365</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.19103</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.16007</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.21056</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.17076</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.22147</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.17043</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.22136</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.22832</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.21031</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21706</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.13098</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.04385</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.44374</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.19684</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>5.999999999999999e-05</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.17122</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16744</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.01033</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04589</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02409</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18698</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.26629</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.08125</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.04722</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.01301</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.04753</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23489</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28073</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25267</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.19854</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32627</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10569</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27315</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.43083</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.25944</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25413</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24381</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.26338</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.28356</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28215</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>-0.04207</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25664</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26982</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.18931</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14344</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.1055</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33215</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.24082</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26386</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27629</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.15523</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>-0.04123</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.18464</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25629</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27405</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.28214</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26754</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.17512</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26168</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26544</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26692</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24801</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28202</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.25241</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.21853</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.2468</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.52266</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.00621</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.44819</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.4927</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40532</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5476799999999999</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.47792</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45549</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43128</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.8507400000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.49969</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42859</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.44593</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40299</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36903</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46769</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.38698</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.46258</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.2093</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17739</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23499</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.25673</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.27507</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.27296</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26159</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19341</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.27672</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39045</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.48964</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46627</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5604199999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.56596</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46216</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5519299999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46521</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.4978</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53306</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52079</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.70002</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.74564</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55036</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55303</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44494</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37687</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26805</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.26693</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26261</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25505</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.23689</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25397</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.19004</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.21211</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13476</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.00437</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.04044</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01277</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.12978</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01194</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02287</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.0242</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23544</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.01552</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02169</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03129</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01541</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02942</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.10464</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06443</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11915</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13808</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16574</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22309</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18125</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.18636</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20763</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.24986</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38747</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41902</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38078</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.7357</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28401</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27603</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27118</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26108</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23263</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22637</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19544</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19543</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.19985</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21572</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>-0.0431</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.02166</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.02378</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.02437</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03612</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07794</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00461</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04428</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.01499</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.01539</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.008880000000000001</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.1554</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.02971</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>-0.02557</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.02844</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22581</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.18214</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.23393</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.26876</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39995</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5281399999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43152</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38522</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.51222</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36279</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41721</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.27147</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.2316</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18628</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.1715</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11241</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.1476</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.17395</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.16128</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08687</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10387</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04755</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.06962</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03648</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03727</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03793999999999999</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03673</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04524</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05136</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.05962</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03453</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05649</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07146</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11397</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.14114</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08605</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.16243</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14391</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08882999999999999</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04606</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21421</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09509999999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.09076000000000001</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18653</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.14023</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16573</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14569</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.18037</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.19929</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.20033</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.2131</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25468</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.25859</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.26013</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.28211</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40419</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27284</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49785</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.41008</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44336</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38215</v>
       </c>
     </row>
   </sheetData>
